--- a/maison_shalom_it_operations_dataset.xlsx
+++ b/maison_shalom_it_operations_dataset.xlsx
@@ -1,37 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ornella\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="7550"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MaisonShalom_IT_Operations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MaisonShalom_IT_Operations" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Active Users</t>
+  </si>
+  <si>
+    <t>Helpdesk Tickets</t>
+  </si>
+  <si>
+    <t>Tickets Resolved</t>
+  </si>
+  <si>
+    <t>Avg Resolution Time (Hours)</t>
+  </si>
+  <si>
+    <t>System Downtime Hours</t>
+  </si>
+  <si>
+    <t>Email Delivery Success Rate</t>
+  </si>
+  <si>
+    <t>Teams Usage %</t>
+  </si>
+  <si>
+    <t>SharePoint Storage Used (GB)</t>
+  </si>
+  <si>
+    <t>Security Incidents</t>
+  </si>
+  <si>
+    <t>Password Resets</t>
+  </si>
+  <si>
+    <t>VPN Users</t>
+  </si>
+  <si>
+    <t>Device Compliance %</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,86 +138,70 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M13" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Percent">
+  <autoFilter ref="A1:M13"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="Month"/>
+    <tableColumn id="2" name="Active Users"/>
+    <tableColumn id="3" name="Helpdesk Tickets"/>
+    <tableColumn id="4" name="Tickets Resolved"/>
+    <tableColumn id="5" name="Avg Resolution Time (Hours)"/>
+    <tableColumn id="6" name="System Downtime Hours"/>
+    <tableColumn id="7" name="Email Delivery Success Rate"/>
+    <tableColumn id="8" name="Teams Usage %"/>
+    <tableColumn id="9" name="SharePoint Storage Used (GB)"/>
+    <tableColumn id="10" name="Security Incidents"/>
+    <tableColumn id="11" name="Password Resets"/>
+    <tableColumn id="12" name="VPN Users"/>
+    <tableColumn id="13" name="Device Compliance %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -412,613 +488,561 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Active Users</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Helpdesk Tickets</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Tickets Resolved</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Resolution Time (Hours)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>System Downtime Hours</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Email Delivery Success Rate</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Teams Usage %</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>SharePoint Storage Used (GB)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Security Incidents</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Password Resets</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>VPN Users</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Device Compliance %</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>145</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>88</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>84</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>5.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>98.2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>68</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>120</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>14</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>45</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>91</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>152</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>92</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>89</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>4.8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>98.7</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>70</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>126</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>48</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>92</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>160</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>105</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>101</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>5.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="G4">
+        <v>97.9</v>
+      </c>
+      <c r="H4">
         <v>73</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>133</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>18</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>52</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>90</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>168</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>111</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>108</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>4.7</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>98.8</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>76</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>141</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>11</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>57</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>93</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>175</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>118</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>114</v>
       </c>
-      <c r="E6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F6">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>98.5</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>78</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>149</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>15</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>60</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>94</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>182</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>123</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>120</v>
       </c>
-      <c r="E7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>99</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>81</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>158</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>65</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>95</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>190</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>130</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>126</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>97.8</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>83</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>170</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>21</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>70</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>91</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>198</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>136</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>131</v>
       </c>
-      <c r="E9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F9">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G9">
+        <v>98.6</v>
+      </c>
+      <c r="H9">
         <v>85</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>182</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>16</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>75</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>93</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>205</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>142</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>138</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>4.3</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="G10">
+        <v>98.9</v>
+      </c>
+      <c r="H10">
         <v>87</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>195</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>13</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>81</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>95</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>214</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>149</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>145</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="G11">
+        <v>99.1</v>
+      </c>
+      <c r="H11">
         <v>89</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>208</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>12</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>88</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>96</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>223</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>156</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>151</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>4.5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>98.7</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>91</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>220</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>15</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>94</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>95</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>235</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>168</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>163</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3.9</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>99.3</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>93</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>235</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>9</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>102</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>97</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>